--- a/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationCartonTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationCartonTemplate.xlsx
@@ -32,13 +32,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -63,6 +56,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -78,6 +78,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -103,10 +110,17 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -583,145 +597,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -729,7 +743,10 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1051,7 +1068,7 @@
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="12.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="23.25" customWidth="1"/>
     <col min="3" max="3" width="14.875" customWidth="1"/>
     <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
@@ -1075,15 +1092,12 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
-      <formula1>"样品归还,三无产品,库存差异调整,赠品入库"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"普通,退货"</formula1>
     </dataValidation>

--- a/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationCartonTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationCartonTemplate.xlsx
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -50,9 +57,6 @@
   </si>
   <si>
     <t>装箱FNSKU</t>
-  </si>
-  <si>
-    <t>数量</t>
   </si>
   <si>
     <r>
@@ -97,6 +101,15 @@
       </rPr>
       <t>货件箱号</t>
     </r>
+  </si>
+  <si>
+    <t>{.boxNo}</t>
+  </si>
+  <si>
+    <t>{.packingSku}</t>
+  </si>
+  <si>
+    <t>{.packingFnSku}</t>
   </si>
 </sst>
 </file>
@@ -727,7 +740,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -738,9 +751,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1065,18 +1075,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="23.25" customWidth="1"/>
     <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1092,16 +1101,20 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
-      <formula1>"普通,退货"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationCartonTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationCartonTemplate.xlsx
@@ -1079,10 +1079,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="23.25" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="3" width="63.75" customWidth="1"/>
+    <col min="4" max="4" width="26.375" customWidth="1"/>
+    <col min="5" max="5" width="25.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationCartonTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationCartonTemplate.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
     <t>装箱SKU</t>
   </si>
   <si>
-    <t>装箱FNSKU</t>
+    <t>装箱FNSKU//装箱三方sku</t>
   </si>
   <si>
     <r>
@@ -1102,7 +1102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
